--- a/data/260629_oa_washout_ct_oa_no_cs/cfus_ct.xlsx
+++ b/data/260629_oa_washout_ct_oa_no_cs/cfus_ct.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">comment</t>
   </si>
   <si>
-    <t xml:space="preserve">M1</t>
+    <t xml:space="preserve">M2</t>
   </si>
   <si>
     <t xml:space="preserve">2|3|2</t>
